--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260513_211809.xlsx
@@ -5586,7 +5586,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
